--- a/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/kapak.xlsx
+++ b/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/kapak.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>YDD R0 06 08 2026 1 MX 1 70 25 114</t>
+          <t>YDD R0 21 09 2026 1 MX 1 76 23 112</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>70 m³/gün</t>
+          <t>75,71 m³/gün</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>350 mg/l</t>
+          <t>300 mg/l</t>
         </is>
       </c>
     </row>
